--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,129 +273,27 @@
     <t>Code du produit de santé</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>fr-lm-produit-sante.medicament.nomProduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>fr-lm-produit-sante.medicament.codeProduit.id</t>
+    <t>Nom du produit (contenant aussi le dosage et la forme galénique)</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.formeGalenique</t>
+  </si>
+  <si>
+    <t>Forme galénique du produit de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.numeroLot</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.codeProduit.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.codeProduit.coding</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.codeProduit.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.codeProduit.autreCodification</t>
-  </si>
-  <si>
-    <t>Produit de santé / Autre codification</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.nomProduit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Nom du produit (contenant aussi le dosage et la forme galénique)</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.formeGalenique</t>
-  </si>
-  <si>
-    <t>Forme galénique du produit de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.numeroLot</t>
   </si>
   <si>
     <t xml:space="preserve">Numéro de lot </t>
@@ -731,13 +629,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.05078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.05078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.14453125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.14453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -748,7 +646,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -762,10 +660,10 @@
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="50.05078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="43.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1178,15 +1076,15 @@
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1194,7 +1092,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1209,13 +1107,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>88</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1266,10 +1164,10 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1283,21 +1181,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1309,17 +1207,15 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>96</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>73</v>
@@ -1356,39 +1252,39 @@
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1399,7 +1295,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1408,23 +1304,19 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>108</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>73</v>
       </c>
@@ -1472,27 +1364,27 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1512,23 +1404,19 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>73</v>
       </c>
@@ -1576,7 +1464,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1588,15 +1476,15 @@
         <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1607,7 +1495,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1619,13 +1507,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1676,13 +1564,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1693,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1704,10 +1592,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1719,13 +1607,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1776,13 +1664,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1793,10 +1681,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1807,7 +1695,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1819,13 +1707,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1876,518 +1764,18 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K12" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="L12" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K14" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="D15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q15" s="2"/>
-      <c r="R15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="175">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -273,36 +273,282 @@
     <t>Code du produit de santé</t>
   </si>
   <si>
-    <t>fr-lm-produit-sante.medicament.nomProduit</t>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.identifyingCodeCodeableConcept</t>
+  </si>
+  <si>
+    <t>Codes du médicament dans une termino spécifique</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.codeProduit.identifyingCodeIdentifier</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>Nom du produit (contenant aussi le dosage et la forme galénique)</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.formeGalenique</t>
-  </si>
-  <si>
-    <t>Forme galénique du produit de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.numeroLot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t>identifiant du medication définition</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.classificationATC</t>
+  </si>
+  <si>
+    <t>Code de regroupement ATC</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.nomProduit</t>
+  </si>
+  <si>
+    <t>Nom du produit (contenant aussi le dosage et la forme galénique). Si le médicament est codé, le nom du produit peut ne pas être renseigné.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.porteurAutorisation</t>
+  </si>
+  <si>
+    <t>Titulaire de l'autorisation de mise sur le marché du médicament. 
+  Cette information est utile pour identifier précisément le produit. Si le produit ne dispose pas d'une autorisation de mise sur le marché, les informations fournies par le fabricant peuvent être utilisées.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.porteurAutorisation.nomPorteurAutorisation</t>
+  </si>
+  <si>
+    <t>Nom de l'organisme détenant l'autorisation de commercialisation/fabrication.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.porteurAutorisation.identifiantPorteurAutorisation</t>
+  </si>
+  <si>
+    <t>Identifiant de l'organisation et/ou de son emplacement physique.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item</t>
+  </si>
+  <si>
+    <t>Dans le cas de conditionnements combinés, il peut s'agir de plusieurs produits fabriqués, chacun disposant de sa propre forme pharmaceutique ainsi que de ses ingrédients et de leurs dosages définis.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.formeGalenique</t>
+  </si>
+  <si>
+    <t>Forme galénique du produit de santé. EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe PDF (forme galénique).</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient</t>
+  </si>
+  <si>
+    <t>Substance active</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.isActive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Numéro de lot </t>
+    <t>Indique si l'ingrédient est considéré comme un ingrédient actif. Les excipients ne sont généralement pas nécessaires et, par défaut, seuls les ingrédients actifs sont attendus.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.substance</t>
+  </si>
+  <si>
+    <t>Substance =&gt; code SMS (2.16.840.1.113883.3.6905.2) de la substance active de l’European Medicines Agency (EMA)</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.infoConcentration</t>
+  </si>
+  <si>
+    <t>concentration par unité</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.infoConcentration.concentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio
+</t>
+  </si>
+  <si>
+    <t>numérateur/dénominateur. Ex 100 mg/1 ml ou 500 mg / comprimé.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.infoConcentration.substanceReferenceConcentration</t>
+  </si>
+  <si>
+    <t>à vérifier</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.quantiteItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>quantité pour 1 item</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.item.ingredient.conditionnement</t>
+  </si>
+  <si>
+    <t>Conditionnement primaire (ampoule, bouteille,…) EDQM Standard Terms (0.4.0.127.0.16.1.1.2.1) / classe CON (Récipient) =&gt; ampoule, blister.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.device</t>
+  </si>
+  <si>
+    <t>Dispositif d'administration inclus dans le produit. Les dispositifs qui ne sont pas contenus dans le conditionnement du médicament ne sont pas pris en compte.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.device.deviceQuantity</t>
+  </si>
+  <si>
+    <t>Nombre de dispositifs.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.device.device[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-dispositif-medical</t>
+  </si>
+  <si>
+    <t>Dispositif codé.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.characteristic</t>
+  </si>
+  <si>
+    <t>Caractéristiques supplémentaires du produit (par ex. sans sucre, bouchon facile à ouvrir, dosage gradué). Il est prévu que les implémenteurs définissent un ensemble de valeurs (ValueSet) adapté à leurs cas d’usage.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.characteristic.type</t>
+  </si>
+  <si>
+    <t>Type de caractéristique</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.characteristic.value[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConceptstringQuantitydateTimeintegerdecimalRatio</t>
+  </si>
+  <si>
+    <t>Valeur de la caractéristique</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.batch</t>
+  </si>
+  <si>
+    <t>Informations relatives au lot d’un médicament. Elles sont généralement enregistrées lors de la dispensation ou de l’administration et sont rarement connues ou pertinentes dans le cadre d’une ordonnance ou d’une demande.</t>
+  </si>
+  <si>
+    <t>fr-lm-produit-sante.medicament.batch.numeroLot</t>
   </si>
   <si>
     <t>Numéro de lot</t>
   </si>
   <si>
-    <t>fr-lm-produit-sante.medicament.dateExpiration</t>
+    <t>fr-lm-produit-sante.medicament.batch.dateExpiration</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -310,24 +556,6 @@
   </si>
   <si>
     <t>Date d'expiration du produit</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.conditionnement</t>
-  </si>
-  <si>
-    <t>Conditionnement</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.equivalentGenerique</t>
-  </si>
-  <si>
-    <t>Code de regroupement ATC</t>
-  </si>
-  <si>
-    <t>fr-lm-produit-sante.medicament.substanceActive</t>
-  </si>
-  <si>
-    <t>Substance active</t>
   </si>
 </sst>
 </file>
@@ -629,24 +857,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.14453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.14453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="81.0" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="81.0" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="72.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -660,10 +888,10 @@
     <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="43.14453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="81.0" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -992,10 +1220,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -1067,24 +1295,24 @@
         <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1092,7 +1320,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>79</v>
@@ -1107,13 +1335,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1164,10 +1392,10 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>79</v>
@@ -1181,21 +1409,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1207,15 +1435,17 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="N6" s="2"/>
+        <v>95</v>
+      </c>
+      <c r="N6" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>73</v>
@@ -1252,39 +1482,39 @@
         <v>73</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1295,7 +1525,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1304,19 +1534,23 @@
         <v>73</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N7" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O7" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="P7" t="s" s="2">
         <v>73</v>
       </c>
@@ -1364,27 +1598,27 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1404,19 +1638,23 @@
         <v>73</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="O8" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P8" t="s" s="2">
         <v>73</v>
       </c>
@@ -1464,7 +1702,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1476,15 +1714,15 @@
         <v>73</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1507,13 +1745,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1564,7 +1802,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1581,10 +1819,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1607,13 +1845,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1664,7 +1902,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1681,10 +1919,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1710,10 +1948,10 @@
         <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1764,7 +2002,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1776,6 +2014,2306 @@
         <v>73</v>
       </c>
       <c r="AJ11" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="M12" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K17" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF18" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-produit-sante.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
